--- a/reservations.xlsx
+++ b/reservations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>First Name</t>
   </si>
@@ -73,10 +73,13 @@
     <t>Schmidt</t>
   </si>
   <si>
-    <t>laura.schmidt@example.com</t>
+    <t>molkamhissen@gmail.com</t>
   </si>
   <si>
     <t>Allemande</t>
+  </si>
+  <si>
+    <t>hotel-palais-bayram</t>
   </si>
   <si>
     <t>Marco</t>
@@ -536,7 +539,7 @@
         <v>46220.0</v>
       </c>
       <c r="G2" s="6">
-        <v>45127.0</v>
+        <v>46223.0</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>13</v>
@@ -562,7 +565,7 @@
         <v>46224.0</v>
       </c>
       <c r="G3" s="6">
-        <v>45121.0</v>
+        <v>46217.0</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>13</v>
@@ -585,30 +588,30 @@
         <v>21</v>
       </c>
       <c r="F4" s="6">
-        <v>46219.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G4" s="6">
-        <v>45132.0</v>
+        <v>46228.0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5">
         <v>32405.0</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="6">
         <v>46226.0</v>
@@ -622,19 +625,19 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="5">
         <v>34706.0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="6">
         <v>46225.0</v>

--- a/reservations.xlsx
+++ b/reservations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>First Name</t>
   </si>
@@ -61,12 +61,15 @@
     <t>Ben Salah</t>
   </si>
   <si>
-    <t>ahmed.bensalah@example.com</t>
+    <t>emnaantigravity@gmail.com</t>
   </si>
   <si>
     <t>Tunisienne</t>
   </si>
   <si>
+    <t>golden-tulip-president-hammamet</t>
+  </si>
+  <si>
     <t>Laura</t>
   </si>
   <si>
@@ -88,7 +91,7 @@
     <t>Rossi</t>
   </si>
   <si>
-    <t>marco.rossi@example.com</t>
+    <t>antigravityemna@gmail.com</t>
   </si>
   <si>
     <t>Italienne</t>
@@ -104,6 +107,18 @@
   </si>
   <si>
     <t>Marocaine</t>
+  </si>
+  <si>
+    <t>Oussema</t>
+  </si>
+  <si>
+    <t>Bouassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@linksprod.com </t>
+  </si>
+  <si>
+    <t>Tunisien</t>
   </si>
 </sst>
 </file>
@@ -562,30 +577,30 @@
         <v>17</v>
       </c>
       <c r="F3" s="6">
-        <v>46224.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G3" s="6">
-        <v>46217.0</v>
+        <v>46221.0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5">
         <v>34123.0</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6">
         <v>46220.0</v>
@@ -594,30 +609,30 @@
         <v>46228.0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5">
         <v>32405.0</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6">
-        <v>46226.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G5" s="6">
-        <v>46221.0</v>
+        <v>46225.0</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>13</v>
@@ -625,19 +640,19 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="5">
         <v>34706.0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="6">
         <v>46225.0</v>
@@ -650,17 +665,34 @@
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5">
+        <v>34706.0</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46221.0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46228.0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
       <c r="E8" s="7"/>
